--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>NAZARIO</t>
+  </si>
+  <si>
     <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>JAFET</t>
@@ -863,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -895,16 +904,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920028</v>
+        <v>20330051920018</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -914,6 +923,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920028</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -82,19 +82,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
   <si>
     <t>JAFET</t>
@@ -547,7 +538,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -556,13 +547,13 @@
         <v>4</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>86.84</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -641,16 +632,19 @@
         <v>34</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>34</v>
       </c>
-      <c r="E2">
-        <v>34</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -664,16 +658,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>33</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H3">
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -684,19 +681,22 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>89.73999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -710,16 +710,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H5">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -810,7 +813,7 @@
         <v>84.62</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,22 +824,22 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>86.84</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -853,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>65.38</v>
+        <v>84.62</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -904,16 +907,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920018</v>
+        <v>21330051920028</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -922,29 +925,6 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920028</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -80,15 +80,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -515,19 +506,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -541,16 +532,16 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>87.18000000000001</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -658,19 +649,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -684,16 +675,16 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H4">
         <v>7.2</v>
@@ -801,19 +792,19 @@
         <v>39</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>84.62</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -827,19 +818,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -875,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -905,29 +896,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920028</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -80,6 +80,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -866,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -896,6 +905,29 @@
         <v>20</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920371</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -787,7 +787,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,10 +82,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>VERA</t>
   </si>
   <si>
+    <t>XICALHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>YAIR</t>
   </si>
   <si>
     <t>ISRAEL</t>
@@ -875,7 +884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,16 +916,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920371</v>
+        <v>22330051920204</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -925,6 +934,29 @@
         <v>12</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920371</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
+++ b/docentes/Zarate Amezcua Eladio Jorge - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -82,19 +82,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
+    <t>PELLICO</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>VERA</t>
   </si>
   <si>
-    <t>XICALHUA</t>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>YAIR</t>
+    <t>JESUS IVAN</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
   </si>
   <si>
     <t>ISRAEL</t>
@@ -822,7 +831,7 @@
         <v>89.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -839,16 +848,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>84.62</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -865,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>84.62</v>
+        <v>80.77</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -884,7 +893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -916,16 +925,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920204</v>
+        <v>22330051920195</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -939,24 +948,47 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920371</v>
+        <v>20330051920071</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920371</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
         <v>26</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
